--- a/Web/TestCasesWeb/Configuracion_fiscal.xlsx
+++ b/Web/TestCasesWeb/Configuracion_fiscal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAD5673-74DF-4FF5-BDE9-8EECC055C6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573BFD59-029E-4FCF-94FA-B26579878B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>Num</t>
   </si>
@@ -61,23 +61,83 @@
     <t>CONFIS004</t>
   </si>
   <si>
-    <t xml:space="preserve">The tax configuration's page </t>
-  </si>
-  <si>
-    <t>1.The user clicks "Configuraición Fiscal"</t>
-  </si>
-  <si>
     <t>1. The tax configuration page is correctly.</t>
   </si>
   <si>
-    <t>Aparace un error: CONFIS001.jpg</t>
+    <t>BLOQUEANTE: Aparace un error,CONFIS001.jpg</t>
+  </si>
+  <si>
+    <t>1.The user clicks "Configuración Fiscal"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The tax configuration page </t>
+  </si>
+  <si>
+    <t>Tax configuration: delete</t>
+  </si>
+  <si>
+    <t>Tax configuration: delete, cancel</t>
+  </si>
+  <si>
+    <t>1. The operation is canceled</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>Tax configuration: Change tax, mandatory fields</t>
+  </si>
+  <si>
+    <t>Tax configuration: Change tax, all fields</t>
+  </si>
+  <si>
+    <t>Tax configuration: Change tax, cancel</t>
+  </si>
+  <si>
+    <t>1. The tax is modified.</t>
+  </si>
+  <si>
+    <t>1. The user selects a tax
+2. Click garbage icon
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user selects a tax
+2. Click garbage icon
+3. Clicks "Aceptar"</t>
+  </si>
+  <si>
+    <t>1. The tax is deleted.</t>
+  </si>
+  <si>
+    <t>1. The user selects a tax
+2. Clicks pencil icon
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user selects a tax 
+2. Clicks pencil icon
+3. Modify all fields
+4. Clicks "Aceptar"</t>
+  </si>
+  <si>
+    <t>1. The user selects a tax 
+2. Clicks pencil icon
+3. Modify mandantory fields
+4. Clicks "Aceptar"</t>
+  </si>
+  <si>
+    <t>CONFIS005</t>
+  </si>
+  <si>
+    <t>CONFIS006</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +159,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -139,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -161,6 +228,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -545,67 +615,135 @@
         <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>16</v>
+      <c r="H2" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="C3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="4"/>
+      <c r="G4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="4"/>
+      <c r="G5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
